--- a/ملف ربط المجموعات الثمانبة بالسور.xlsx
+++ b/ملف ربط المجموعات الثمانبة بالسور.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Quran_Analysis_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A196B181-BB85-4863-B3B8-A9CC53A9F608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F8ABEB-8E8B-4716-89D1-38143FE84AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{373ED9EA-B9FF-4805-837A-3CA574F4AE69}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{373ED9EA-B9FF-4805-837A-3CA574F4AE69}"/>
   </bookViews>
   <sheets>
     <sheet name="ملف ربط السور بالمجموعات" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ملف ربط السور بالمجموعات'!$A$1:$E$115</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="219">
   <si>
     <t>م</t>
   </si>
@@ -676,6 +679,12 @@
   </si>
   <si>
     <t>رقم المجموعة</t>
+  </si>
+  <si>
+    <t>تبدأ من سورة رقم</t>
+  </si>
+  <si>
+    <t>تنتهى بسورة رقم</t>
   </si>
 </sst>
 </file>
@@ -775,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -792,10 +801,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -808,6 +813,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1122,13 +1128,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB13CD06-41A0-4A1D-B16A-4D0C775DD8C9}">
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="7.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1141,11 +1148,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -1155,14 +1162,14 @@
       <c r="C2" s="3">
         <v>7</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1172,14 +1179,24 @@
       <c r="C3" s="4">
         <v>286</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="8">
         <v>2</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I3" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -1189,14 +1206,26 @@
       <c r="C4" s="3">
         <v>200</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>50</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I4" s="10">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10">
+        <v>5</v>
+      </c>
+      <c r="L4" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -1206,14 +1235,26 @@
       <c r="C5" s="4">
         <v>176</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>76</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I5" s="10">
+        <v>2</v>
+      </c>
+      <c r="J5" s="10">
+        <v>6</v>
+      </c>
+      <c r="K5" s="10">
+        <v>6</v>
+      </c>
+      <c r="L5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -1223,14 +1264,27 @@
       <c r="C6" s="4">
         <v>120</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>106</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I6" s="10">
+        <v>3</v>
+      </c>
+      <c r="J6" s="10">
+        <v>7</v>
+      </c>
+      <c r="K6" s="10">
+        <v>12</v>
+      </c>
+      <c r="L6" s="10">
+        <f>K6-J6+1</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1240,14 +1294,27 @@
       <c r="C7" s="4">
         <v>165</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="8">
         <v>128</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I7" s="10">
+        <v>4</v>
+      </c>
+      <c r="J7" s="10">
+        <v>13</v>
+      </c>
+      <c r="K7" s="10">
+        <v>18</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" ref="L7:L11" si="0">K7-J7+1</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
@@ -1257,14 +1324,27 @@
       <c r="C8" s="4">
         <v>206</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="8">
         <v>151</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I8" s="10">
+        <v>5</v>
+      </c>
+      <c r="J8" s="10">
+        <v>19</v>
+      </c>
+      <c r="K8" s="10">
+        <v>28</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
@@ -1274,14 +1354,27 @@
       <c r="C9" s="4">
         <v>75</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <v>177</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I9" s="10">
+        <v>6</v>
+      </c>
+      <c r="J9" s="10">
+        <v>29</v>
+      </c>
+      <c r="K9" s="10">
+        <v>36</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
@@ -1291,14 +1384,27 @@
       <c r="C10" s="4">
         <v>129</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="8">
         <v>187</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I10" s="10">
+        <v>7</v>
+      </c>
+      <c r="J10" s="10">
+        <v>37</v>
+      </c>
+      <c r="K10" s="10">
+        <v>56</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
@@ -1308,14 +1414,27 @@
       <c r="C11" s="4">
         <v>109</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="8">
         <v>208</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I11" s="10">
+        <v>8</v>
+      </c>
+      <c r="J11" s="10">
+        <v>57</v>
+      </c>
+      <c r="K11" s="10">
+        <v>114</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
@@ -1325,14 +1444,18 @@
       <c r="C12" s="4">
         <v>123</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="8">
         <v>221</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <f>SUM(L4:L11)</f>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1342,14 +1465,14 @@
       <c r="C13" s="5">
         <v>111</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="9">
         <v>235</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
@@ -1359,14 +1482,14 @@
       <c r="C14" s="5">
         <v>43</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9">
         <v>249</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
@@ -1376,14 +1499,14 @@
       <c r="C15" s="3">
         <v>52</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>255</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1393,10 +1516,10 @@
       <c r="C16" s="3">
         <v>99</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>262</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="7">
         <v>4</v>
       </c>
     </row>
@@ -1410,10 +1533,10 @@
       <c r="C17" s="5">
         <v>128</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="9">
         <v>267</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="7">
         <v>4</v>
       </c>
     </row>
@@ -1427,10 +1550,10 @@
       <c r="C18" s="5">
         <v>111</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="9">
         <v>282</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="7">
         <v>4</v>
       </c>
     </row>
@@ -1444,10 +1567,10 @@
       <c r="C19" s="5">
         <v>110</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="9">
         <v>293</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="7">
         <v>4</v>
       </c>
     </row>
@@ -1461,10 +1584,10 @@
       <c r="C20" s="3">
         <v>98</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="6">
         <v>305</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1478,10 +1601,10 @@
       <c r="C21" s="3">
         <v>135</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="6">
         <v>312</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1495,10 +1618,10 @@
       <c r="C22" s="3">
         <v>112</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>322</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1512,10 +1635,10 @@
       <c r="C23" s="3">
         <v>78</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="6">
         <v>332</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1529,10 +1652,10 @@
       <c r="C24" s="3">
         <v>118</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="6">
         <v>342</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1546,10 +1669,10 @@
       <c r="C25" s="5">
         <v>64</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="9">
         <v>350</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1563,10 +1686,10 @@
       <c r="C26" s="5">
         <v>77</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="9">
         <v>359</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1580,10 +1703,10 @@
       <c r="C27" s="5">
         <v>227</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="9">
         <v>367</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1597,10 +1720,10 @@
       <c r="C28" s="5">
         <v>93</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="9">
         <v>377</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1614,10 +1737,10 @@
       <c r="C29" s="5">
         <v>88</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="9">
         <v>385</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1631,10 +1754,10 @@
       <c r="C30" s="5">
         <v>69</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="9">
         <v>396</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1648,10 +1771,10 @@
       <c r="C31" s="3">
         <v>60</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="6">
         <v>404</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1665,10 +1788,10 @@
       <c r="C32" s="3">
         <v>34</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="6">
         <v>411</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1682,10 +1805,10 @@
       <c r="C33" s="3">
         <v>30</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="6">
         <v>415</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1699,10 +1822,10 @@
       <c r="C34" s="5">
         <v>73</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="9">
         <v>418</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1716,10 +1839,10 @@
       <c r="C35" s="5">
         <v>54</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="9">
         <v>428</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1733,10 +1856,10 @@
       <c r="C36" s="3">
         <v>45</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="6">
         <v>434</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1750,10 +1873,10 @@
       <c r="C37" s="5">
         <v>83</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="9">
         <v>440</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1767,10 +1890,10 @@
       <c r="C38" s="5">
         <v>182</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="9">
         <v>446</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="7">
         <v>6</v>
       </c>
     </row>
@@ -1784,10 +1907,10 @@
       <c r="C39" s="3">
         <v>88</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="6">
         <v>453</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1801,10 +1924,10 @@
       <c r="C40" s="5">
         <v>75</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="9">
         <v>458</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1818,10 +1941,10 @@
       <c r="C41" s="5">
         <v>85</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="9">
         <v>467</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1835,10 +1958,10 @@
       <c r="C42" s="5">
         <v>54</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="9">
         <v>477</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1852,10 +1975,10 @@
       <c r="C43" s="3">
         <v>53</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="6">
         <v>483</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1869,10 +1992,10 @@
       <c r="C44" s="5">
         <v>89</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="9">
         <v>489</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1886,10 +2009,10 @@
       <c r="C45" s="3">
         <v>59</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="6">
         <v>496</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1903,10 +2026,10 @@
       <c r="C46" s="3">
         <v>37</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="6">
         <v>499</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1920,10 +2043,10 @@
       <c r="C47" s="3">
         <v>35</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="6">
         <v>502</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1937,10 +2060,10 @@
       <c r="C48" s="3">
         <v>38</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="6">
         <v>507</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1954,10 +2077,10 @@
       <c r="C49" s="5">
         <v>29</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="9">
         <v>511</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1971,10 +2094,10 @@
       <c r="C50" s="3">
         <v>18</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="6">
         <v>515</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="7">
         <v>7</v>
       </c>
     </row>
@@ -1988,10 +2111,10 @@
       <c r="C51" s="3">
         <v>45</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="6">
         <v>518</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="7">
         <v>7</v>
       </c>
     </row>
@@ -2005,10 +2128,10 @@
       <c r="C52" s="5">
         <v>60</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="6">
         <v>520</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="7">
         <v>7</v>
       </c>
     </row>
@@ -2022,10 +2145,10 @@
       <c r="C53" s="3">
         <v>49</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="6">
         <v>523</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="7">
         <v>7</v>
       </c>
     </row>
@@ -2039,10 +2162,10 @@
       <c r="C54" s="3">
         <v>62</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="6">
         <v>526</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="7">
         <v>7</v>
       </c>
     </row>
@@ -2056,10 +2179,10 @@
       <c r="C55" s="3">
         <v>55</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="6">
         <v>528</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="7">
         <v>7</v>
       </c>
     </row>
@@ -2073,10 +2196,10 @@
       <c r="C56" s="3">
         <v>78</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="6">
         <v>531</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="7">
         <v>7</v>
       </c>
     </row>
@@ -2090,10 +2213,10 @@
       <c r="C57" s="3">
         <v>96</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="6">
         <v>534</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="7">
         <v>7</v>
       </c>
     </row>
@@ -2107,10 +2230,10 @@
       <c r="C58" s="3">
         <v>29</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="6">
         <v>537</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2124,10 +2247,10 @@
       <c r="C59" s="3">
         <v>22</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="6">
         <v>542</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2141,10 +2264,10 @@
       <c r="C60" s="3">
         <v>24</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="6">
         <v>545</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2158,10 +2281,10 @@
       <c r="C61" s="3">
         <v>13</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="6">
         <v>549</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2175,10 +2298,10 @@
       <c r="C62" s="3">
         <v>14</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="6">
         <v>551</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2192,10 +2315,10 @@
       <c r="C63" s="3">
         <v>11</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="6">
         <v>553</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2209,10 +2332,10 @@
       <c r="C64" s="3">
         <v>11</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="6">
         <v>554</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2226,10 +2349,10 @@
       <c r="C65" s="3">
         <v>18</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="6">
         <v>556</v>
       </c>
-      <c r="E65" s="9">
+      <c r="E65" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2243,10 +2366,10 @@
       <c r="C66" s="3">
         <v>12</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="6">
         <v>558</v>
       </c>
-      <c r="E66" s="9">
+      <c r="E66" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2260,10 +2383,10 @@
       <c r="C67" s="3">
         <v>12</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="6">
         <v>560</v>
       </c>
-      <c r="E67" s="9">
+      <c r="E67" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2277,10 +2400,10 @@
       <c r="C68" s="3">
         <v>30</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="6">
         <v>562</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E68" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2294,10 +2417,10 @@
       <c r="C69" s="3">
         <v>52</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="6">
         <v>564</v>
       </c>
-      <c r="E69" s="9">
+      <c r="E69" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2311,10 +2434,10 @@
       <c r="C70" s="3">
         <v>52</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="6">
         <v>566</v>
       </c>
-      <c r="E70" s="9">
+      <c r="E70" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2328,10 +2451,10 @@
       <c r="C71" s="3">
         <v>44</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="6">
         <v>568</v>
       </c>
-      <c r="E71" s="9">
+      <c r="E71" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2345,10 +2468,10 @@
       <c r="C72" s="3">
         <v>28</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="6">
         <v>570</v>
       </c>
-      <c r="E72" s="9">
+      <c r="E72" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2362,10 +2485,10 @@
       <c r="C73" s="3">
         <v>28</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="6">
         <v>572</v>
       </c>
-      <c r="E73" s="9">
+      <c r="E73" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2379,10 +2502,10 @@
       <c r="C74" s="3">
         <v>20</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="6">
         <v>574</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2396,10 +2519,10 @@
       <c r="C75" s="3">
         <v>56</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="6">
         <v>575</v>
       </c>
-      <c r="E75" s="9">
+      <c r="E75" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2413,10 +2536,10 @@
       <c r="C76" s="3">
         <v>40</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="6">
         <v>577</v>
       </c>
-      <c r="E76" s="9">
+      <c r="E76" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2430,10 +2553,10 @@
       <c r="C77" s="3">
         <v>31</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="6">
         <v>578</v>
       </c>
-      <c r="E77" s="9">
+      <c r="E77" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2447,10 +2570,10 @@
       <c r="C78" s="3">
         <v>50</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="6">
         <v>580</v>
       </c>
-      <c r="E78" s="9">
+      <c r="E78" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2464,10 +2587,10 @@
       <c r="C79" s="3">
         <v>40</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="6">
         <v>582</v>
       </c>
-      <c r="E79" s="9">
+      <c r="E79" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2481,10 +2604,10 @@
       <c r="C80" s="3">
         <v>46</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="6">
         <v>583</v>
       </c>
-      <c r="E80" s="9">
+      <c r="E80" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2498,10 +2621,10 @@
       <c r="C81" s="3">
         <v>42</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="6">
         <v>585</v>
       </c>
-      <c r="E81" s="9">
+      <c r="E81" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2515,10 +2638,10 @@
       <c r="C82" s="3">
         <v>29</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="6">
         <v>586</v>
       </c>
-      <c r="E82" s="9">
+      <c r="E82" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2532,10 +2655,10 @@
       <c r="C83" s="3">
         <v>19</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="6">
         <v>587</v>
       </c>
-      <c r="E83" s="9">
+      <c r="E83" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2549,10 +2672,10 @@
       <c r="C84" s="3">
         <v>36</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="6">
         <v>587</v>
       </c>
-      <c r="E84" s="9">
+      <c r="E84" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2566,10 +2689,10 @@
       <c r="C85" s="3">
         <v>25</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="6">
         <v>589</v>
       </c>
-      <c r="E85" s="9">
+      <c r="E85" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2583,10 +2706,10 @@
       <c r="C86" s="3">
         <v>22</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="6">
         <v>590</v>
       </c>
-      <c r="E86" s="9">
+      <c r="E86" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2600,10 +2723,10 @@
       <c r="C87" s="3">
         <v>17</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="6">
         <v>591</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E87" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2617,10 +2740,10 @@
       <c r="C88" s="3">
         <v>19</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="6">
         <v>591</v>
       </c>
-      <c r="E88" s="9">
+      <c r="E88" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2634,10 +2757,10 @@
       <c r="C89" s="3">
         <v>26</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="6">
         <v>592</v>
       </c>
-      <c r="E89" s="9">
+      <c r="E89" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2651,10 +2774,10 @@
       <c r="C90" s="3">
         <v>30</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="6">
         <v>593</v>
       </c>
-      <c r="E90" s="9">
+      <c r="E90" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2668,10 +2791,10 @@
       <c r="C91" s="3">
         <v>20</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="6">
         <v>594</v>
       </c>
-      <c r="E91" s="9">
+      <c r="E91" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2685,10 +2808,10 @@
       <c r="C92" s="3">
         <v>15</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="6">
         <v>595</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2702,10 +2825,10 @@
       <c r="C93" s="3">
         <v>21</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="6">
         <v>595</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E93" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2719,10 +2842,10 @@
       <c r="C94" s="3">
         <v>11</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="6">
         <v>596</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2736,10 +2859,10 @@
       <c r="C95" s="3">
         <v>8</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="6">
         <v>596</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2753,10 +2876,10 @@
       <c r="C96" s="3">
         <v>8</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="6">
         <v>597</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2770,10 +2893,10 @@
       <c r="C97" s="3">
         <v>19</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="6">
         <v>597</v>
       </c>
-      <c r="E97" s="9">
+      <c r="E97" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2787,10 +2910,10 @@
       <c r="C98" s="3">
         <v>5</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="6">
         <v>598</v>
       </c>
-      <c r="E98" s="9">
+      <c r="E98" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2804,10 +2927,10 @@
       <c r="C99" s="3">
         <v>8</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="6">
         <v>598</v>
       </c>
-      <c r="E99" s="9">
+      <c r="E99" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2821,10 +2944,10 @@
       <c r="C100" s="3">
         <v>8</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="6">
         <v>599</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2838,10 +2961,10 @@
       <c r="C101" s="3">
         <v>11</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="6">
         <v>599</v>
       </c>
-      <c r="E101" s="9">
+      <c r="E101" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2855,10 +2978,10 @@
       <c r="C102" s="3">
         <v>11</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="6">
         <v>600</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2872,10 +2995,10 @@
       <c r="C103" s="3">
         <v>8</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="6">
         <v>600</v>
       </c>
-      <c r="E103" s="9">
+      <c r="E103" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2889,10 +3012,10 @@
       <c r="C104" s="3">
         <v>3</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D104" s="6">
         <v>601</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2906,10 +3029,10 @@
       <c r="C105" s="3">
         <v>9</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="6">
         <v>601</v>
       </c>
-      <c r="E105" s="9">
+      <c r="E105" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2923,10 +3046,10 @@
       <c r="C106" s="3">
         <v>5</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="6">
         <v>601</v>
       </c>
-      <c r="E106" s="9">
+      <c r="E106" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2940,10 +3063,10 @@
       <c r="C107" s="3">
         <v>4</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="6">
         <v>602</v>
       </c>
-      <c r="E107" s="9">
+      <c r="E107" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2957,10 +3080,10 @@
       <c r="C108" s="3">
         <v>7</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="6">
         <v>602</v>
       </c>
-      <c r="E108" s="9">
+      <c r="E108" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2974,10 +3097,10 @@
       <c r="C109" s="3">
         <v>3</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="6">
         <v>602</v>
       </c>
-      <c r="E109" s="9">
+      <c r="E109" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2991,10 +3114,10 @@
       <c r="C110" s="3">
         <v>6</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="6">
         <v>603</v>
       </c>
-      <c r="E110" s="9">
+      <c r="E110" s="7">
         <v>8</v>
       </c>
     </row>
@@ -3008,10 +3131,10 @@
       <c r="C111" s="3">
         <v>3</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="6">
         <v>603</v>
       </c>
-      <c r="E111" s="9">
+      <c r="E111" s="7">
         <v>8</v>
       </c>
     </row>
@@ -3025,10 +3148,10 @@
       <c r="C112" s="3">
         <v>5</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="6">
         <v>603</v>
       </c>
-      <c r="E112" s="9">
+      <c r="E112" s="7">
         <v>8</v>
       </c>
     </row>
@@ -3042,10 +3165,10 @@
       <c r="C113" s="3">
         <v>4</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="6">
         <v>604</v>
       </c>
-      <c r="E113" s="9">
+      <c r="E113" s="7">
         <v>8</v>
       </c>
     </row>
@@ -3059,10 +3182,10 @@
       <c r="C114" s="3">
         <v>5</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="6">
         <v>604</v>
       </c>
-      <c r="E114" s="9">
+      <c r="E114" s="7">
         <v>8</v>
       </c>
     </row>
@@ -3076,14 +3199,15 @@
       <c r="C115" s="3">
         <v>6</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="6">
         <v>604</v>
       </c>
-      <c r="E115" s="9">
+      <c r="E115" s="7">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E115" xr:uid="{CB13CD06-41A0-4A1D-B16A-4D0C775DD8C9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>